--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Table1_OP_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Table1_OP_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -396,12 +396,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>allied health professional</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>52054 (30.79%)</t>
+          <t>31430 (18.59%)</t>
         </is>
       </c>
     </row>
@@ -418,7 +418,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15824 (9.36%)</t>
+          <t>14864 (8.83%)</t>
         </is>
       </c>
     </row>
@@ -435,7 +435,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11730 (6.94%)</t>
+          <t>12539 (7.42%)</t>
         </is>
       </c>
     </row>
@@ -447,12 +447,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>rheumatology</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5380 (3.18%)</t>
+          <t>11609 (6.87%)</t>
         </is>
       </c>
     </row>
@@ -464,12 +464,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>cardiology</t>
+          <t>radiology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4309 (2.55%)</t>
+          <t>5881 (3.48%)</t>
         </is>
       </c>
     </row>
@@ -481,12 +481,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>geriatric medicine</t>
+          <t>rheumatology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4137 (2.45%)</t>
+          <t>5236 (3.1%)</t>
         </is>
       </c>
     </row>
@@ -498,12 +498,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>general medical practice</t>
+          <t>clinical haematology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3118 (1.84%)</t>
+          <t>4577 (2.71%)</t>
         </is>
       </c>
     </row>
@@ -515,12 +515,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dermatology</t>
+          <t>cardiology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2835 (1.68%)</t>
+          <t>4419 (2.61%)</t>
         </is>
       </c>
     </row>
@@ -532,12 +532,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>neurology</t>
+          <t>general surgery</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2659 (1.57%)</t>
+          <t>3844 (2.27%)</t>
         </is>
       </c>
     </row>
@@ -549,12 +549,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>respiratory medicine</t>
+          <t>rehabilitation medicine</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2504 (1.48%)</t>
+          <t>3224 (1.91%)</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ear nose and throat</t>
+          <t>geriatric medicine</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2449 (1.45%)</t>
+          <t>3208 (1.9%)</t>
         </is>
       </c>
     </row>
@@ -583,12 +583,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gynaecology</t>
+          <t>general medical practice</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2016 (1.19%)</t>
+          <t>3118 (1.84%)</t>
         </is>
       </c>
     </row>
@@ -600,12 +600,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>radiology</t>
+          <t>dermatology</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2004 (1.19%)</t>
+          <t>2835 (1.68%)</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>general surgery</t>
+          <t>gynaecology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1923 (1.14%)</t>
+          <t>2215 (1.31%)</t>
         </is>
       </c>
     </row>
@@ -639,75 +639,75 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1813 (1.07%)</t>
+          <t>1957 (1.16%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OP Health Care Service Status</t>
+          <t>Main Specialty</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>neurology</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20512 (89.57%)</t>
+          <t>1916 (1.13%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OP Health Care Service Status</t>
+          <t>Main Specialty</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Non-User</t>
+          <t>audio vestibular medicine</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2388 (10.43%)</t>
+          <t>1883 (1.11%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Treatment Specialty</t>
+          <t>OP Health Care Service Status</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>trauma and orthopaedic service</t>
+          <t>User</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>54293 (32.12%)</t>
+          <t>20512 (89.57%)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Treatment Specialty</t>
+          <t>OP Health Care Service Status</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Non-User</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>26615 (15.74%)</t>
+          <t>2388 (10.43%)</t>
         </is>
       </c>
     </row>
@@ -719,12 +719,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>physiotherapy service</t>
+          <t>trauma and orthopaedic service</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>26485 (15.67%)</t>
+          <t>54293 (32.12%)</t>
         </is>
       </c>
     </row>
@@ -736,12 +736,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Other Treatment Specialty</t>
+          <t>physiotherapy service</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16127 (9.55%)</t>
+          <t>26485 (15.67%)</t>
         </is>
       </c>
     </row>
@@ -753,12 +753,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ophthalmology service</t>
+          <t>Other Treatment Specialty</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>11730 (6.94%)</t>
+          <t>23231 (13.74%)</t>
         </is>
       </c>
     </row>
@@ -770,12 +770,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>diagnostic imaging service</t>
+          <t>ophthalmology service</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5698 (3.37%)</t>
+          <t>11730 (6.94%)</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>rheumatology service</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5236 (3.1%)</t>
+          <t>11609 (6.87%)</t>
         </is>
       </c>
     </row>
@@ -804,12 +804,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>cardiology service</t>
+          <t>diagnostic imaging service</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>4309 (2.55%)</t>
+          <t>5698 (3.37%)</t>
         </is>
       </c>
     </row>
@@ -821,12 +821,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>anticoagulant service</t>
+          <t>rheumatology service</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2976 (1.76%)</t>
+          <t>5236 (3.1%)</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>dermatology service</t>
+          <t>cardiology service</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2835 (1.68%)</t>
+          <t>4309 (2.55%)</t>
         </is>
       </c>
     </row>
@@ -855,12 +855,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>occupational therapy service</t>
+          <t>elderly medicine service</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2747 (1.62%)</t>
+          <t>3208 (1.9%)</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ear nose and throat service</t>
+          <t>general internal medicine service</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2449 (1.45%)</t>
+          <t>3118 (1.84%)</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gynaecology service</t>
+          <t>anticoagulant service</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2016 (1.19%)</t>
+          <t>2976 (1.76%)</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>general surgery service</t>
+          <t>dermatology service</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1923 (1.14%)</t>
+          <t>2835 (1.68%)</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gastroenterology service</t>
+          <t>occupational therapy service</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1813 (1.07%)</t>
+          <t>2747 (1.62%)</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,92 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1796 (1.06%)</t>
+          <t>2238 (1.32%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Treatment Specialty</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>gynaecology service</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2016 (1.19%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Treatment Specialty</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>general surgery service</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1923 (1.14%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Treatment Specialty</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>audiology service</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1883 (1.11%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Treatment Specialty</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>gastroenterology service</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1813 (1.07%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Treatment Specialty</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>neurology service</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1700 (1.01%)</t>
         </is>
       </c>
     </row>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Table1_OP_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Table1_OP_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -418,7 +418,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14864 (8.83%)</t>
+          <t>16549 (9.83%)</t>
         </is>
       </c>
     </row>
@@ -447,12 +447,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>radiology</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11609 (6.87%)</t>
+          <t>5881 (3.48%)</t>
         </is>
       </c>
     </row>
@@ -464,12 +464,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>radiology</t>
+          <t>rheumatology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5881 (3.48%)</t>
+          <t>5236 (3.1%)</t>
         </is>
       </c>
     </row>
@@ -481,12 +481,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rheumatology</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5236 (3.1%)</t>
+          <t>4957 (2.93%)</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3224 (1.91%)</t>
+          <t>3228 (1.91%)</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>gynaecology</t>
+          <t>respiratory medicine</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2215 (1.31%)</t>
+          <t>2514 (1.49%)</t>
         </is>
       </c>
     </row>
@@ -634,12 +634,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>gastroenterology</t>
+          <t>ear nose and throat</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1957 (1.16%)</t>
+          <t>2449 (1.45%)</t>
         </is>
       </c>
     </row>
@@ -651,12 +651,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>neurology</t>
+          <t>gynaecology</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1916 (1.13%)</t>
+          <t>2215 (1.31%)</t>
         </is>
       </c>
     </row>
@@ -668,80 +668,80 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>audio vestibular medicine</t>
+          <t>gastroenterology</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1883 (1.11%)</t>
+          <t>1957 (1.16%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OP Health Care Service Status</t>
+          <t>Main Specialty</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>neurology</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>20512 (89.57%)</t>
+          <t>1916 (1.13%)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OP Health Care Service Status</t>
+          <t>Main Specialty</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Non-User</t>
+          <t>audio vestibular medicine</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2388 (10.43%)</t>
+          <t>1883 (1.11%)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Treatment Specialty</t>
+          <t>OP Health Care Service Status</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>trauma and orthopaedic service</t>
+          <t>User</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>54293 (32.12%)</t>
+          <t>20512 (89.57%)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Treatment Specialty</t>
+          <t>OP Health Care Service Status</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>physiotherapy service</t>
+          <t>Non-User</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>26485 (15.67%)</t>
+          <t>2388 (10.43%)</t>
         </is>
       </c>
     </row>
@@ -753,12 +753,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Other Treatment Specialty</t>
+          <t>trauma and orthopaedic service</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>23231 (13.74%)</t>
+          <t>54293 (32.12%)</t>
         </is>
       </c>
     </row>
@@ -770,12 +770,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ophthalmology service</t>
+          <t>physiotherapy service</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>11730 (6.94%)</t>
+          <t>26485 (15.67%)</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Other Treatment Specialty</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>11609 (6.87%)</t>
+          <t>24930 (14.75%)</t>
         </is>
       </c>
     </row>
@@ -804,12 +804,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>diagnostic imaging service</t>
+          <t>ophthalmology service</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5698 (3.37%)</t>
+          <t>11730 (6.94%)</t>
         </is>
       </c>
     </row>
@@ -821,12 +821,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>rheumatology service</t>
+          <t>diagnostic imaging service</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5236 (3.1%)</t>
+          <t>5698 (3.37%)</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>cardiology service</t>
+          <t>rheumatology service</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>4309 (2.55%)</t>
+          <t>5236 (3.1%)</t>
         </is>
       </c>
     </row>
@@ -855,12 +855,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>elderly medicine service</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3208 (1.9%)</t>
+          <t>4957 (2.93%)</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>general internal medicine service</t>
+          <t>cardiology service</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3118 (1.84%)</t>
+          <t>4309 (2.55%)</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>anticoagulant service</t>
+          <t>elderly medicine service</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2976 (1.76%)</t>
+          <t>3208 (1.9%)</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>dermatology service</t>
+          <t>general internal medicine service</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2835 (1.68%)</t>
+          <t>3118 (1.84%)</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>occupational therapy service</t>
+          <t>anticoagulant service</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2747 (1.62%)</t>
+          <t>2976 (1.76%)</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>intermediate care service</t>
+          <t>dermatology service</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2238 (1.32%)</t>
+          <t>2835 (1.68%)</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>gynaecology service</t>
+          <t>occupational therapy service</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2016 (1.19%)</t>
+          <t>2747 (1.62%)</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>general surgery service</t>
+          <t>respiratory medicine service</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1923 (1.14%)</t>
+          <t>2504 (1.48%)</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>audiology service</t>
+          <t>ear nose and throat service</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1883 (1.11%)</t>
+          <t>2449 (1.45%)</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>gastroenterology service</t>
+          <t>intermediate care service</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1813 (1.07%)</t>
+          <t>2238 (1.32%)</t>
         </is>
       </c>
     </row>
@@ -1025,10 +1025,78 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>gynaecology service</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2016 (1.19%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Treatment Specialty</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>general surgery service</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1923 (1.14%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Treatment Specialty</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>audiology service</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1883 (1.11%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Treatment Specialty</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>gastroenterology service</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1813 (1.07%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Treatment Specialty</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>neurology service</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>1700 (1.01%)</t>
         </is>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Table1_OP_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Table1_OP_OMOP.xlsx
@@ -401,7 +401,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31430 (18.59%)</t>
+          <t>32486 (19.22%)</t>
         </is>
       </c>
     </row>
@@ -418,7 +418,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16549 (9.83%)</t>
+          <t>16825 (9.98%)</t>
         </is>
       </c>
     </row>
@@ -435,7 +435,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12539 (7.42%)</t>
+          <t>12664 (7.49%)</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5881 (3.48%)</t>
+          <t>6002 (3.55%)</t>
         </is>
       </c>
     </row>
@@ -481,12 +481,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>clinical haematology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4957 (2.93%)</t>
+          <t>4577 (2.71%)</t>
         </is>
       </c>
     </row>
@@ -498,12 +498,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>clinical haematology</t>
+          <t>cardiology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4577 (2.71%)</t>
+          <t>4419 (2.61%)</t>
         </is>
       </c>
     </row>
@@ -515,12 +515,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>cardiology</t>
+          <t>general surgery</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4419 (2.61%)</t>
+          <t>3844 (2.27%)</t>
         </is>
       </c>
     </row>
@@ -532,12 +532,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>general surgery</t>
+          <t>rehabilitation medicine</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3844 (2.27%)</t>
+          <t>3629 (2.15%)</t>
         </is>
       </c>
     </row>
@@ -549,12 +549,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>rehabilitation medicine</t>
+          <t>geriatric medicine</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3228 (1.91%)</t>
+          <t>3208 (1.9%)</t>
         </is>
       </c>
     </row>
@@ -566,12 +566,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>geriatric medicine</t>
+          <t>general medical practice</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3208 (1.9%)</t>
+          <t>3118 (1.84%)</t>
         </is>
       </c>
     </row>
@@ -583,12 +583,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>general medical practice</t>
+          <t>dermatology</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3118 (1.84%)</t>
+          <t>2835 (1.68%)</t>
         </is>
       </c>
     </row>
@@ -600,12 +600,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>dermatology</t>
+          <t>respiratory medicine</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2835 (1.68%)</t>
+          <t>2514 (1.49%)</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>respiratory medicine</t>
+          <t>ear nose and throat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2514 (1.49%)</t>
+          <t>2449 (1.45%)</t>
         </is>
       </c>
     </row>
@@ -634,12 +634,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ear nose and throat</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2449 (1.45%)</t>
+          <t>2431 (1.44%)</t>
         </is>
       </c>
     </row>
@@ -651,12 +651,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>gynaecology</t>
+          <t>audio vestibular medicine</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2215 (1.31%)</t>
+          <t>2430 (1.44%)</t>
         </is>
       </c>
     </row>
@@ -668,12 +668,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gastroenterology</t>
+          <t>gynaecology</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1957 (1.16%)</t>
+          <t>2215 (1.31%)</t>
         </is>
       </c>
     </row>
@@ -685,12 +685,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>neurology</t>
+          <t>gastroenterology</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1916 (1.13%)</t>
+          <t>1957 (1.16%)</t>
         </is>
       </c>
     </row>
@@ -702,12 +702,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>audio vestibular medicine</t>
+          <t>neurology</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1883 (1.11%)</t>
+          <t>1916 (1.13%)</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>24930 (14.75%)</t>
+          <t>25409 (15.03%)</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>11730 (6.94%)</t>
+          <t>11855 (7.01%)</t>
         </is>
       </c>
     </row>
@@ -855,12 +855,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>general internal medicine service</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4957 (2.93%)</t>
+          <t>4483 (2.65%)</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>general internal medicine service</t>
+          <t>anticoagulant service</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3118 (1.84%)</t>
+          <t>2976 (1.76%)</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>anticoagulant service</t>
+          <t>dermatology service</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2976 (1.76%)</t>
+          <t>2835 (1.68%)</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>dermatology service</t>
+          <t>occupational therapy service</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2835 (1.68%)</t>
+          <t>2747 (1.62%)</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>occupational therapy service</t>
+          <t>respiratory medicine service</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2747 (1.62%)</t>
+          <t>2504 (1.48%)</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>respiratory medicine service</t>
+          <t>ear nose and throat service</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2504 (1.48%)</t>
+          <t>2449 (1.45%)</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ear nose and throat service</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2449 (1.45%)</t>
+          <t>2431 (1.44%)</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>intermediate care service</t>
+          <t>audiology service</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2238 (1.32%)</t>
+          <t>2430 (1.44%)</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>gynaecology service</t>
+          <t>intermediate care service</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2016 (1.19%)</t>
+          <t>2248 (1.33%)</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>general surgery service</t>
+          <t>gynaecology service</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1923 (1.14%)</t>
+          <t>2016 (1.19%)</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>audiology service</t>
+          <t>general surgery service</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1883 (1.11%)</t>
+          <t>1923 (1.14%)</t>
         </is>
       </c>
     </row>

--- a/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Table1_OP_OMOP.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/OP/Table1_OP_OMOP.xlsx
@@ -418,7 +418,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16825 (9.98%)</t>
+          <t>16808 (9.97%)</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4577 (2.71%)</t>
+          <t>4594 (2.72%)</t>
         </is>
       </c>
     </row>
